--- a/SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor/SHT40-IP67-RS485_RS485-TTL_USB-TTL.xlsx
+++ b/SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor/SHT40-IP67-RS485_RS485-TTL_USB-TTL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\Github\longhoney\KhaoSat_RS485-Modbus\SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\Github\longhoney\KhaoSat_RS485-Modbus_1\SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4737AFE5-AD38-4B76-BB58-4D81EA883B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7C3BF5-BF22-4C96-8B65-B4003F57537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read_Data" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>Address code</t>
   </si>
@@ -216,9 +216,6 @@
     <t>Value of Baudrate</t>
   </si>
   <si>
-    <t>{01}{03}{02}{00}{01}{79}{84}</t>
-  </si>
-  <si>
     <t>Địa chỉ: 1- 254</t>
   </si>
   <si>
@@ -301,6 +298,12 @@
   </si>
   <si>
     <t>(Chỉ 3 cái nên có thể dò với lệnh đọc địa chỉ là đủ)</t>
+  </si>
+  <si>
+    <t>{07}{03}{02}{00}{07}{71}{86}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.binaryhexconverter.com/decimal-to-hex-converter </t>
   </si>
 </sst>
 </file>
@@ -532,7 +535,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -552,6 +555,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -570,18 +590,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -589,15 +597,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -898,7 +899,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -930,34 +931,34 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="22"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="17"/>
+      <c r="C4" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="23"/>
+      <c r="G4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="19" t="s">
+      <c r="H4" s="23"/>
+      <c r="I4" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="20"/>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
+      <c r="A5" s="17"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="25"/>
       <c r="I5" s="6" t="s">
         <v>36</v>
       </c>
@@ -966,7 +967,7 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="22"/>
+      <c r="A6" s="17"/>
       <c r="C6" s="8" t="s">
         <v>54</v>
       </c>
@@ -986,10 +987,10 @@
         <v>6</v>
       </c>
       <c r="I6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>67</v>
       </c>
       <c r="M6" t="s">
         <v>11</v>
@@ -1002,10 +1003,10 @@
       <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="25"/>
+      <c r="I7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="16"/>
       <c r="M7" t="s">
         <v>39</v>
       </c>
@@ -1022,10 +1023,10 @@
         <v>10</v>
       </c>
       <c r="H8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" t="s">
         <v>87</v>
-      </c>
-      <c r="K8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -1053,7 +1054,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -1090,36 +1091,36 @@
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21" t="s">
+      <c r="G14" s="15"/>
+      <c r="H14" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21" t="s">
+      <c r="I14" s="15"/>
+      <c r="J14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K14" s="21"/>
+      <c r="K14" s="15"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
       <c r="J15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1173,7 +1174,7 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B21" t="s">
@@ -1205,34 +1206,34 @@
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="17"/>
+      <c r="C22" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="15" t="s">
+      <c r="F22" s="23"/>
+      <c r="G22" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="19" t="s">
+      <c r="H22" s="23"/>
+      <c r="I22" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="20"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="22"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+      <c r="A23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="25"/>
       <c r="I23" s="6" t="s">
         <v>36</v>
       </c>
@@ -1241,7 +1242,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="22"/>
+      <c r="A24" s="17"/>
       <c r="C24" s="8" t="s">
         <v>54</v>
       </c>
@@ -1261,18 +1262,18 @@
         <v>2</v>
       </c>
       <c r="I24" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B25" s="3"/>
-      <c r="I25" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="J25" s="25"/>
+      <c r="I25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
@@ -1286,7 +1287,7 @@
         <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.5">
@@ -1317,7 +1318,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
@@ -1350,30 +1351,30 @@
       <c r="A32" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="24"/>
-      <c r="H32" s="19" t="s">
+      <c r="G32" s="27"/>
+      <c r="H32" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="I32" s="20"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="24"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="6" t="s">
         <v>36</v>
       </c>
@@ -1422,7 +1423,7 @@
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B39" t="s">
@@ -1454,34 +1455,34 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A40" s="22"/>
-      <c r="C40" s="13" t="s">
+      <c r="A40" s="17"/>
+      <c r="C40" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="15" t="s">
+      <c r="F40" s="23"/>
+      <c r="G40" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="16"/>
-      <c r="I40" s="19" t="s">
+      <c r="H40" s="23"/>
+      <c r="I40" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J40" s="20"/>
+      <c r="J40" s="19"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41" s="22"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="18"/>
+      <c r="A41" s="17"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="25"/>
       <c r="I41" s="6" t="s">
         <v>36</v>
       </c>
@@ -1490,7 +1491,7 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A42" s="22"/>
+      <c r="A42" s="17"/>
       <c r="C42" s="8" t="s">
         <v>54</v>
       </c>
@@ -1510,18 +1511,18 @@
         <v>2</v>
       </c>
       <c r="I42" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="B43" s="3"/>
-      <c r="I43" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="J43" s="25"/>
+      <c r="I43" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J43" s="16"/>
     </row>
     <row r="44" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
@@ -1535,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="H44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="21" x14ac:dyDescent="0.5">
@@ -1566,7 +1567,7 @@
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -1599,30 +1600,30 @@
       <c r="A50" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D50" s="21" t="s">
+      <c r="D50" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="21" t="s">
+      <c r="E50" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="19" t="s">
+      <c r="G50" s="15"/>
+      <c r="H50" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="I50" s="20"/>
+      <c r="I50" s="19"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
       <c r="H51" s="6" t="s">
         <v>36</v>
       </c>
@@ -1662,6 +1663,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:F41"/>
+    <mergeCell ref="G40:H41"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:G51"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:F23"/>
+    <mergeCell ref="G22:H23"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:G33"/>
+    <mergeCell ref="H32:I32"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="I25:J25"/>
@@ -1678,27 +1700,6 @@
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="A39:A42"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:G33"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:F23"/>
-    <mergeCell ref="G22:H23"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:G51"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:F41"/>
-    <mergeCell ref="G40:H41"/>
-    <mergeCell ref="I40:J40"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -1720,11 +1721,11 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -1756,34 +1757,34 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22"/>
-      <c r="C3" s="13" t="s">
+      <c r="A3" s="17"/>
+      <c r="C3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="19" t="s">
+      <c r="H3" s="23"/>
+      <c r="I3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="20"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="22"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="17"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="25"/>
       <c r="I4" s="6" t="s">
         <v>36</v>
       </c>
@@ -1792,7 +1793,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
+      <c r="A5" s="17"/>
       <c r="C5" s="8" t="s">
         <v>54</v>
       </c>
@@ -1822,14 +1823,14 @@
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" s="26"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
@@ -1844,27 +1845,30 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
     </row>
-    <row r="10" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
-      <c r="P10" s="28"/>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
@@ -1873,7 +1877,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -1909,32 +1913,32 @@
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="15" t="s">
+      <c r="F14" s="23"/>
+      <c r="G14" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="19" t="s">
+      <c r="H14" s="23"/>
+      <c r="I14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="20"/>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="25"/>
       <c r="I15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1980,11 +1984,11 @@
     <row r="19" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B21" t="s">
@@ -2016,34 +2020,34 @@
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="17"/>
+      <c r="C22" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="15" t="s">
+      <c r="F22" s="23"/>
+      <c r="G22" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="19" t="s">
+      <c r="H22" s="23"/>
+      <c r="I22" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="20"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="22"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+      <c r="A23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="25"/>
       <c r="I23" s="6" t="s">
         <v>36</v>
       </c>
@@ -2052,7 +2056,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="22"/>
+      <c r="A24" s="17"/>
       <c r="C24" s="8" t="s">
         <v>2</v>
       </c>
@@ -2072,24 +2076,24 @@
         <v>2</v>
       </c>
       <c r="I24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="C25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="J25" s="26"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="28"/>
     </row>
     <row r="26" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
@@ -2109,22 +2113,22 @@
       <c r="A28" s="7"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
@@ -2133,7 +2137,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
@@ -2169,32 +2173,32 @@
       <c r="A33" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="16"/>
-      <c r="G33" s="15" t="s">
+      <c r="F33" s="23"/>
+      <c r="G33" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="19" t="s">
+      <c r="H33" s="23"/>
+      <c r="I33" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J33" s="20"/>
+      <c r="J33" s="19"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="25"/>
       <c r="I34" s="6" t="s">
         <v>36</v>
       </c>
@@ -2238,14 +2242,15 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="G3:H4"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:F15"/>
@@ -2255,16 +2260,18 @@
     <mergeCell ref="D22:D23"/>
     <mergeCell ref="E22:F23"/>
     <mergeCell ref="G22:H23"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:F4"/>
-    <mergeCell ref="G3:H4"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J33"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{12BD2609-7915-4B96-828E-BBF6EE96881F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2284,7 +2291,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -2316,34 +2323,34 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="22"/>
-      <c r="C3" s="13" t="s">
+      <c r="A3" s="17"/>
+      <c r="C3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="19" t="s">
+      <c r="H3" s="23"/>
+      <c r="I3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="20"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="22"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="17"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="25"/>
       <c r="I4" s="6" t="s">
         <v>36</v>
       </c>
@@ -2352,7 +2359,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="22"/>
+      <c r="A5" s="17"/>
       <c r="C5" s="8" t="s">
         <v>25</v>
       </c>
@@ -2382,10 +2389,10 @@
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
@@ -2396,23 +2403,23 @@
         <v>FF 03 07 D0 00 01 91 59</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -2421,7 +2428,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -2454,30 +2461,30 @@
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="19" t="s">
+      <c r="G13" s="23"/>
+      <c r="H13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="20"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="18"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="6" t="s">
         <v>36</v>
       </c>
@@ -2488,7 +2495,7 @@
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C15" s="5" t="str">
         <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$11,"{",""),"}",""),(COLUMN(A11)-1)*2+1,2)</f>
-        <v>0x01</v>
+        <v>0x07</v>
       </c>
       <c r="D15" s="5" t="str">
         <f t="shared" ref="D15:I15" si="0">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$11,"{",""),"}",""),(COLUMN(B11)-1)*2+1,2)</f>
@@ -2504,40 +2511,31 @@
       </c>
       <c r="G15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x01</v>
+        <v>0x07</v>
       </c>
       <c r="H15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x79</v>
+        <v>0x71</v>
       </c>
       <c r="I15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+        <v>0x86</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A22" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B23" t="s">
@@ -2568,38 +2566,38 @@
         <v>7</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="22"/>
-      <c r="C24" s="13" t="s">
+      <c r="A24" s="17"/>
+      <c r="C24" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="15" t="s">
+      <c r="F24" s="23"/>
+      <c r="G24" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="19" t="s">
+      <c r="H24" s="23"/>
+      <c r="I24" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J24" s="20"/>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" s="22"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
+      <c r="A25" s="17"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="25"/>
       <c r="I25" s="6" t="s">
         <v>36</v>
       </c>
@@ -2608,7 +2606,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A26" s="22"/>
+      <c r="A26" s="17"/>
       <c r="C26" s="8" t="s">
         <v>25</v>
       </c>
@@ -2638,12 +2636,12 @@
       <c r="C27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26" t="s">
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="J27" s="26"/>
+      <c r="J27" s="28"/>
     </row>
     <row r="28" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
@@ -2655,22 +2653,22 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
@@ -2679,7 +2677,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -2712,30 +2710,30 @@
       <c r="A34" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="19" t="s">
+      <c r="G34" s="23"/>
+      <c r="H34" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="20"/>
+      <c r="I34" s="19"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="18"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
       <c r="H35" s="6" t="s">
         <v>36</v>
       </c>
@@ -2780,19 +2778,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:G35"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:F25"/>
-    <mergeCell ref="G24:H25"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="A2:A5"/>
@@ -2806,6 +2791,19 @@
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:F25"/>
+    <mergeCell ref="G24:H25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:G35"/>
+    <mergeCell ref="H34:I34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2857,14 +2855,14 @@
       <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="19" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="20"/>
+      <c r="H3" s="19"/>
       <c r="I3" s="6" t="s">
         <v>23</v>
       </c>

--- a/SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor/SHT40-IP67-RS485_RS485-TTL_USB-TTL.xlsx
+++ b/SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor/SHT40-IP67-RS485_RS485-TTL_USB-TTL.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\Github\longhoney\KhaoSat_RS485-Modbus_1\SHT-RS485-Modbus-RTU-Temperature-Humidity-Sensor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7C3BF5-BF22-4C96-8B65-B4003F57537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64EF121-B799-4550-AAC2-E6F3C2B0EE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Read_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Config" sheetId="2" r:id="rId2"/>
-    <sheet name="Scan" sheetId="4" r:id="rId3"/>
-    <sheet name="F_Reset" sheetId="3" r:id="rId4"/>
+    <sheet name="Calib" sheetId="5" r:id="rId2"/>
+    <sheet name="Config" sheetId="2" r:id="rId3"/>
+    <sheet name="Scan" sheetId="4" r:id="rId4"/>
+    <sheet name="F_Reset" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="117">
   <si>
     <t>Address code</t>
   </si>
@@ -189,15 +190,9 @@
     <t>Value Address</t>
   </si>
   <si>
-    <t>Đổi sang 0x05</t>
-  </si>
-  <si>
     <t>0x05</t>
   </si>
   <si>
-    <t>0x49</t>
-  </si>
-  <si>
     <t>0xD1</t>
   </si>
   <si>
@@ -219,21 +214,6 @@
     <t>Địa chỉ: 1- 254</t>
   </si>
   <si>
-    <t>{01}{03}{02}{00}{02}{39}{85}</t>
-  </si>
-  <si>
-    <t>CRC = 0x8FC5</t>
-  </si>
-  <si>
-    <t>0xC5</t>
-  </si>
-  <si>
-    <t>0x8F</t>
-  </si>
-  <si>
-    <t>{05}{03}{04}{01}{FC}{01}{19}{BE}{65}</t>
-  </si>
-  <si>
     <t>CRC = 0x4ED4</t>
   </si>
   <si>
@@ -243,9 +223,6 @@
     <t>0x4E</t>
   </si>
   <si>
-    <t>{05}{03}{02}{01}{18}{48}{1E}</t>
-  </si>
-  <si>
     <t>CRC = 0x8E85</t>
   </si>
   <si>
@@ -258,9 +235,6 @@
     <t>{05}{03}{02}{01}{F9}{88}{56}</t>
   </si>
   <si>
-    <t>CRC = 0x0349</t>
-  </si>
-  <si>
     <t>{05}{06}{07}{D0}{00}{01}{49}{03}</t>
   </si>
   <si>
@@ -300,10 +274,112 @@
     <t>(Chỉ 3 cái nên có thể dò với lệnh đọc địa chỉ là đủ)</t>
   </si>
   <si>
-    <t>{07}{03}{02}{00}{07}{71}{86}</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.binaryhexconverter.com/decimal-to-hex-converter </t>
+  </si>
+  <si>
+    <t>Đọc giá trị hiệu chỉnh nhiệt độ</t>
+  </si>
+  <si>
+    <t>Địa chỉ thanh ghi: 0x0050</t>
+  </si>
+  <si>
+    <t>0x50</t>
+  </si>
+  <si>
+    <t>CRC = 0x1B84</t>
+  </si>
+  <si>
+    <t>0x84</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
+    <t>0x08</t>
+  </si>
+  <si>
+    <t>Đổi sang 0x01</t>
+  </si>
+  <si>
+    <t>CRC = 0x1E48</t>
+  </si>
+  <si>
+    <t>0x48</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
+    <t>01 06 07 D1 00 01 19 47</t>
+  </si>
+  <si>
+    <t>{01}{03}{02}{00}{01}{79}{84}</t>
+  </si>
+  <si>
+    <t>{01}{03}{02}{00}{00}{B8}{44}</t>
+  </si>
+  <si>
+    <t>Đọc giá trị hiệu chỉnh độ ẩm</t>
+  </si>
+  <si>
+    <t>Địa chỉ thanh ghi: 0x0051</t>
+  </si>
+  <si>
+    <t>0x51</t>
+  </si>
+  <si>
+    <t>CRC = 0xDBD5</t>
+  </si>
+  <si>
+    <t>0xD5</t>
+  </si>
+  <si>
+    <t>0xDB</t>
+  </si>
+  <si>
+    <t>01 03 00 51 00 01 D5 DB</t>
+  </si>
+  <si>
+    <t>{01}{03}{02}{01}{2F}{F8}{08}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.binaryhexconverter.com/hex-to-decimal-converter </t>
+  </si>
+  <si>
+    <t>{01}{03}{04}{02}{7D}{01}{30}{6A}{17}</t>
+  </si>
+  <si>
+    <t>Ghi đè giá trị hiệu chỉnh nhiệt độ</t>
+  </si>
+  <si>
+    <t>Offset?</t>
+  </si>
+  <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>01 06 00 50 00 00 89 DB</t>
+  </si>
+  <si>
+    <t>0xF6</t>
+  </si>
+  <si>
+    <t>0x027D = 637 = 63.7%</t>
+  </si>
+  <si>
+    <t>0x0130 = 304 = 30.4 do C</t>
+  </si>
+  <si>
+    <t>CRC = 0x6D48</t>
+  </si>
+  <si>
+    <t>0x6D</t>
+  </si>
+  <si>
+    <t>Giá trị gốc + giá trị hiệu chỉnh = giá trị đo được</t>
+  </si>
+  <si>
+    <t>0xABCD = XYZ = XY.Z độ C. Nếu tăng 5 thì cộng Z thêm 5. Nếu tăng 10 thì cộng Y thêm 1. Nếu tăng 100 thì cộng Y thêm 1</t>
   </si>
 </sst>
 </file>
@@ -535,7 +611,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -557,21 +633,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -590,6 +651,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -597,8 +670,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -880,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
@@ -899,7 +976,7 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
@@ -931,45 +1008,48 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="C4" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="A4" s="24"/>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="22" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="18" t="s">
+      <c r="H4" s="18"/>
+      <c r="I4" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="22"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="25"/>
+      <c r="A5" s="24"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="6" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="M5" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="17"/>
+      <c r="A6" s="24"/>
       <c r="C6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>3</v>
@@ -987,10 +1067,10 @@
         <v>6</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s">
         <v>11</v>
@@ -1003,10 +1083,10 @@
       <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="16"/>
+      <c r="I7" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="27"/>
       <c r="M7" t="s">
         <v>39</v>
       </c>
@@ -1017,16 +1097,16 @@
       </c>
       <c r="B8" t="str">
         <f>TRIM(MID(C6,3,2)&amp;" "&amp;MID(D6,3,2)&amp;" "&amp;MID(E6,3,2)&amp;" "&amp;MID(F6,3,2)&amp;" "&amp;MID(G6,3,2)&amp;" "&amp;MID(H6,3,2)&amp;" "&amp;MID(I6,3,2)&amp;" "&amp;MID(J6,3,2))</f>
-        <v>05 03 00 00 00 02 C5 8F</v>
+        <v>05 03 00 00 00 02 48 1E</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K8" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -1054,7 +1134,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -1091,36 +1171,36 @@
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="C14" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15" t="s">
+      <c r="I14" s="23"/>
+      <c r="J14" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="K14" s="15"/>
+      <c r="K14" s="23"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
       <c r="J15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1131,7 +1211,7 @@
     <row r="16" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C16" s="5" t="str">
         <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$12,"{",""),"}",""),(COLUMN(A12)-1)*2+1,2)</f>
-        <v>0x05</v>
+        <v>0x01</v>
       </c>
       <c r="D16" s="5" t="str">
         <f t="shared" ref="D16:H16" si="0">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$12,"{",""),"}",""),(COLUMN(B12)-1)*2+1,2)</f>
@@ -1143,11 +1223,11 @@
       </c>
       <c r="F16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x01</v>
+        <v>0x02</v>
       </c>
       <c r="G16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0xFC</v>
+        <v>0x7D</v>
       </c>
       <c r="H16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -1155,539 +1235,536 @@
       </c>
       <c r="I16" s="5" t="str">
         <f t="shared" ref="I16" si="1">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$12,"{",""),"}",""),(COLUMN(G12)-1)*2+1,2)</f>
-        <v>0x19</v>
+        <v>0x30</v>
       </c>
       <c r="J16" s="5" t="str">
         <f t="shared" ref="J16" si="2">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$12,"{",""),"}",""),(COLUMN(H12)-1)*2+1,2)</f>
-        <v>0xBE</v>
+        <v>0x6A</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" ref="K16" si="3">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$12,"{",""),"}",""),(COLUMN(I12)-1)*2+1,2)</f>
-        <v>0x65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+        <v>0x17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="19" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:16" ht="21" x14ac:dyDescent="0.5">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B21" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E22" s="5">
         <v>2</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F22" s="5">
         <v>3</v>
       </c>
-      <c r="G21" s="5">
-        <v>4</v>
-      </c>
-      <c r="H21" s="5">
-        <v>5</v>
-      </c>
-      <c r="I21" s="5">
+      <c r="G22" s="5">
+        <v>4</v>
+      </c>
+      <c r="H22" s="5">
+        <v>5</v>
+      </c>
+      <c r="I22" s="5">
         <v>6</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J22" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="17"/>
-      <c r="C22" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="20" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="24"/>
+      <c r="C23" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E23" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="22" t="s">
+      <c r="F23" s="18"/>
+      <c r="G23" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="23"/>
-      <c r="I22" s="18" t="s">
+      <c r="H23" s="18"/>
+      <c r="I23" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="19"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="17"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="6" t="s">
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="24"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J24" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="17"/>
-      <c r="C24" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="8" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="24"/>
+      <c r="C25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="8" t="s">
+      <c r="E25" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="8" t="s">
+      <c r="G25" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B25" s="3"/>
-      <c r="I25" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="I25" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B26" s="3"/>
+      <c r="I26" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="str">
-        <f>TRIM(MID(C24,3,2)&amp;" "&amp;MID(D24,3,2)&amp;" "&amp;MID(E24,3,2)&amp;" "&amp;MID(F24,3,2)&amp;" "&amp;MID(G24,3,2)&amp;" "&amp;MID(H24,3,2)&amp;" "&amp;MID(I24,3,2)&amp;" "&amp;MID(J24,3,2))</f>
+      <c r="B27" t="str">
+        <f>TRIM(MID(C25,3,2)&amp;" "&amp;MID(D25,3,2)&amp;" "&amp;MID(E25,3,2)&amp;" "&amp;MID(F25,3,2)&amp;" "&amp;MID(G25,3,2)&amp;" "&amp;MID(H25,3,2)&amp;" "&amp;MID(I25,3,2)&amp;" "&amp;MID(J25,3,2))</f>
         <v>05 03 00 01 00 01 D4 4E</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G27" t="s">
         <v>10</v>
       </c>
-      <c r="H26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="3"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
+      <c r="H27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>71</v>
-      </c>
-    </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="5">
-        <v>0</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5">
         <v>1</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E32" s="5">
         <v>2</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F32" s="5">
         <v>3</v>
       </c>
-      <c r="G31" s="5">
-        <v>4</v>
-      </c>
-      <c r="H31" s="5">
-        <v>5</v>
-      </c>
-      <c r="I31" s="5">
+      <c r="G32" s="5">
+        <v>4</v>
+      </c>
+      <c r="H32" s="5">
+        <v>5</v>
+      </c>
+      <c r="I32" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32" s="15" t="s">
+      <c r="C33" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E33" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F33" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G32" s="27"/>
-      <c r="H32" s="18" t="s">
+      <c r="G33" s="26"/>
+      <c r="H33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I32" s="19"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="6" t="s">
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I34" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C34" s="5" t="str">
-        <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$30,"{",""),"}",""),(COLUMN(A30)-1)*2+1,2)</f>
-        <v>0x05</v>
-      </c>
-      <c r="D34" s="5" t="str">
-        <f t="shared" ref="D34:I34" si="4">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$30,"{",""),"}",""),(COLUMN(B30)-1)*2+1,2)</f>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C35" s="5" t="str">
+        <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$31,"{",""),"}",""),(COLUMN(A31)-1)*2+1,2)</f>
+        <v>0x01</v>
+      </c>
+      <c r="D35" s="5" t="str">
+        <f t="shared" ref="D35:I35" si="4">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$31,"{",""),"}",""),(COLUMN(B31)-1)*2+1,2)</f>
         <v>0x03</v>
       </c>
-      <c r="E34" s="5" t="str">
+      <c r="E35" s="5" t="str">
         <f t="shared" si="4"/>
         <v>0x02</v>
       </c>
-      <c r="F34" s="5" t="str">
+      <c r="F35" s="5" t="str">
         <f t="shared" si="4"/>
         <v>0x01</v>
       </c>
-      <c r="G34" s="5" t="str">
+      <c r="G35" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>0x18</v>
-      </c>
-      <c r="H34" s="5" t="str">
+        <v>0x2F</v>
+      </c>
+      <c r="H35" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>0x48</v>
-      </c>
-      <c r="I34" s="5" t="str">
+        <v>0xF8</v>
+      </c>
+      <c r="I35" s="5" t="str">
         <f t="shared" si="4"/>
-        <v>0x1E</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="21" x14ac:dyDescent="0.5">
-      <c r="B35" s="3"/>
-    </row>
-    <row r="36" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+        <v>0x08</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B36" s="3"/>
+    </row>
     <row r="37" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="1:16" ht="21" x14ac:dyDescent="0.5">
-      <c r="B38" s="3" t="s">
+    <row r="38" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B39" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39" s="17" t="s">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B39" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="5">
-        <v>0</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" s="5">
+        <v>0</v>
+      </c>
+      <c r="D40" s="5">
         <v>1</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E40" s="5">
         <v>2</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F40" s="5">
         <v>3</v>
       </c>
-      <c r="G39" s="5">
-        <v>4</v>
-      </c>
-      <c r="H39" s="5">
-        <v>5</v>
-      </c>
-      <c r="I39" s="5">
+      <c r="G40" s="5">
+        <v>4</v>
+      </c>
+      <c r="H40" s="5">
+        <v>5</v>
+      </c>
+      <c r="I40" s="5">
         <v>6</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J40" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A40" s="17"/>
-      <c r="C40" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="20" t="s">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="24"/>
+      <c r="C41" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E41" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="23"/>
-      <c r="G40" s="22" t="s">
+      <c r="F41" s="18"/>
+      <c r="G41" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="23"/>
-      <c r="I40" s="18" t="s">
+      <c r="H41" s="18"/>
+      <c r="I41" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J40" s="19"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41" s="17"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="6" t="s">
+      <c r="J41" s="22"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A42" s="24"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J41" s="6" t="s">
+      <c r="J42" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A42" s="17"/>
-      <c r="C42" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="8" t="s">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A43" s="24"/>
+      <c r="C43" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="8" t="s">
+      <c r="E43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="I42" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="21" x14ac:dyDescent="0.5">
-      <c r="B43" s="3"/>
-      <c r="I43" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="J43" s="16"/>
-    </row>
-    <row r="44" spans="1:16" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="7" t="s">
+      <c r="I43" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B44" s="3"/>
+      <c r="I44" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="J44" s="27"/>
+    </row>
+    <row r="45" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B44" t="str">
-        <f>TRIM(MID(C42,3,2)&amp;" "&amp;MID(D42,3,2)&amp;" "&amp;MID(E42,3,2)&amp;" "&amp;MID(F42,3,2)&amp;" "&amp;MID(G42,3,2)&amp;" "&amp;MID(H42,3,2)&amp;" "&amp;MID(I42,3,2)&amp;" "&amp;MID(J42,3,2))</f>
+      <c r="B45" t="str">
+        <f>TRIM(MID(C43,3,2)&amp;" "&amp;MID(D43,3,2)&amp;" "&amp;MID(E43,3,2)&amp;" "&amp;MID(F43,3,2)&amp;" "&amp;MID(G43,3,2)&amp;" "&amp;MID(H43,3,2)&amp;" "&amp;MID(I43,3,2)&amp;" "&amp;MID(J43,3,2))</f>
         <v>05 03 00 00 00 01 85 8E</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G45" t="s">
         <v>10</v>
       </c>
-      <c r="H44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="21" x14ac:dyDescent="0.5">
-      <c r="B45" s="3"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="12"/>
-      <c r="P46" s="12"/>
+      <c r="H45" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B46" s="3"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12"/>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>75</v>
-      </c>
-    </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B49" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" s="5">
-        <v>0</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="5">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5">
         <v>1</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E50" s="5">
         <v>2</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F50" s="5">
         <v>3</v>
       </c>
-      <c r="G49" s="5">
-        <v>4</v>
-      </c>
-      <c r="H49" s="5">
-        <v>5</v>
-      </c>
-      <c r="I49" s="5">
+      <c r="G50" s="5">
+        <v>4</v>
+      </c>
+      <c r="H50" s="5">
+        <v>5</v>
+      </c>
+      <c r="I50" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="15" t="s">
+      <c r="C51" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E51" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F51" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G50" s="15"/>
-      <c r="H50" s="18" t="s">
+      <c r="G51" s="23"/>
+      <c r="H51" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I50" s="19"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="6" t="s">
+      <c r="I51" s="22"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I52" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C52" s="5" t="str">
-        <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$48,"{",""),"}",""),(COLUMN(A48)-1)*2+1,2)</f>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C53" s="5" t="str">
+        <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$49,"{",""),"}",""),(COLUMN(A49)-1)*2+1,2)</f>
         <v>0x05</v>
       </c>
-      <c r="D52" s="5" t="str">
-        <f t="shared" ref="D52:I52" si="5">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$48,"{",""),"}",""),(COLUMN(B48)-1)*2+1,2)</f>
+      <c r="D53" s="5" t="str">
+        <f t="shared" ref="D53:I53" si="5">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$49,"{",""),"}",""),(COLUMN(B49)-1)*2+1,2)</f>
         <v>0x03</v>
       </c>
-      <c r="E52" s="5" t="str">
+      <c r="E53" s="5" t="str">
         <f t="shared" si="5"/>
         <v>0x02</v>
       </c>
-      <c r="F52" s="5" t="str">
+      <c r="F53" s="5" t="str">
         <f t="shared" si="5"/>
         <v>0x01</v>
       </c>
-      <c r="G52" s="5" t="str">
+      <c r="G53" s="5" t="str">
         <f t="shared" si="5"/>
         <v>0xF9</v>
       </c>
-      <c r="H52" s="5" t="str">
+      <c r="H53" s="5" t="str">
         <f t="shared" si="5"/>
         <v>0x88</v>
       </c>
-      <c r="I52" s="5" t="str">
+      <c r="I53" s="5" t="str">
         <f t="shared" si="5"/>
         <v>0x56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:F41"/>
-    <mergeCell ref="G40:H41"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="F50:G51"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:F23"/>
-    <mergeCell ref="G22:H23"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:G33"/>
-    <mergeCell ref="H32:I32"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I44:J44"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C4:C5"/>
@@ -1699,18 +1776,706 @@
     <mergeCell ref="F14:G15"/>
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:G34"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:F24"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:G52"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:F42"/>
+    <mergeCell ref="G41:H42"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G7" r:id="rId1" xr:uid="{F9610125-9B04-4658-8300-728703DC5B34}"/>
+    <hyperlink ref="M5" r:id="rId2" xr:uid="{A22DFD32-0B64-4DBC-BA2E-F03DDC8370E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC41C9A-3C62-4986-9A3E-AC9BB028E4CE}">
+  <dimension ref="A1:P42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B1" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5">
+        <v>3</v>
+      </c>
+      <c r="G2" s="5">
+        <v>4</v>
+      </c>
+      <c r="H2" s="5">
+        <v>5</v>
+      </c>
+      <c r="I2" s="5">
+        <v>6</v>
+      </c>
+      <c r="J2" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="24"/>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="18"/>
+      <c r="I3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="22"/>
+      <c r="M3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="24"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="24"/>
+      <c r="C5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B6" s="3"/>
+      <c r="I6" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="27"/>
+    </row>
+    <row r="7" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="str">
+        <f>TRIM(MID(C5,3,2)&amp;" "&amp;MID(D5,3,2)&amp;" "&amp;MID(E5,3,2)&amp;" "&amp;MID(F5,3,2)&amp;" "&amp;MID(G5,3,2)&amp;" "&amp;MID(H5,3,2)&amp;" "&amp;MID(I5,3,2)&amp;" "&amp;MID(J5,3,2))</f>
+        <v>01 03 00 50 00 01 84 1B</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4</v>
+      </c>
+      <c r="H11" s="5">
+        <v>5</v>
+      </c>
+      <c r="I11" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="26"/>
+      <c r="H12" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C14" s="5" t="str">
+        <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(A10)-1)*2+1,2)</f>
+        <v>0x01</v>
+      </c>
+      <c r="D14" s="5" t="str">
+        <f t="shared" ref="D14:I14" si="0">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(B10)-1)*2+1,2)</f>
+        <v>0x03</v>
+      </c>
+      <c r="E14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0x02</v>
+      </c>
+      <c r="F14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0x00</v>
+      </c>
+      <c r="G14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0x00</v>
+      </c>
+      <c r="H14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0xB8</v>
+      </c>
+      <c r="I14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>0x44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B17" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5">
+        <v>3</v>
+      </c>
+      <c r="G18" s="5">
+        <v>4</v>
+      </c>
+      <c r="H18" s="5">
+        <v>5</v>
+      </c>
+      <c r="I18" s="5">
+        <v>6</v>
+      </c>
+      <c r="J18" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" s="24"/>
+      <c r="C19" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="22"/>
+      <c r="M19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="24"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="24"/>
+      <c r="C21" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.5">
+      <c r="B22" s="3"/>
+      <c r="I22" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="str">
+        <f>TRIM(MID(C21,3,2)&amp;" "&amp;MID(D21,3,2)&amp;" "&amp;MID(E21,3,2)&amp;" "&amp;MID(F21,3,2)&amp;" "&amp;MID(G21,3,2)&amp;" "&amp;MID(H21,3,2)&amp;" "&amp;MID(I21,3,2)&amp;" "&amp;MID(J21,3,2))</f>
+        <v>01 03 00 51 00 01 D5 DB</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5">
+        <v>2</v>
+      </c>
+      <c r="F27" s="5">
+        <v>3</v>
+      </c>
+      <c r="G27" s="5">
+        <v>4</v>
+      </c>
+      <c r="H27" s="5">
+        <v>5</v>
+      </c>
+      <c r="I27" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="23"/>
+      <c r="H28" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" s="22"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="C30" s="5" t="str">
+        <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(A26)-1)*2+1,2)</f>
+        <v>0x01</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f t="shared" ref="D30" si="1">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(B26)-1)*2+1,2)</f>
+        <v>0x03</v>
+      </c>
+      <c r="E30" s="5" t="str">
+        <f t="shared" ref="E30" si="2">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(C26)-1)*2+1,2)</f>
+        <v>0x02</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f t="shared" ref="F30" si="3">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(D26)-1)*2+1,2)</f>
+        <v>0x00</v>
+      </c>
+      <c r="G30" s="5" t="str">
+        <f t="shared" ref="G30" si="4">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(E26)-1)*2+1,2)</f>
+        <v>0x00</v>
+      </c>
+      <c r="H30" s="5" t="str">
+        <f t="shared" ref="H30" si="5">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(F26)-1)*2+1,2)</f>
+        <v>0xB8</v>
+      </c>
+      <c r="I30" s="5" t="str">
+        <f t="shared" ref="I30" si="6">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$10,"{",""),"}",""),(COLUMN(G26)-1)*2+1,2)</f>
+        <v>0x44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="1:10" ht="21" x14ac:dyDescent="0.5">
+      <c r="B33" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2</v>
+      </c>
+      <c r="F34" s="5">
+        <v>3</v>
+      </c>
+      <c r="G34" s="5">
+        <v>4</v>
+      </c>
+      <c r="H34" s="5">
+        <v>5</v>
+      </c>
+      <c r="I34" s="5">
+        <v>6</v>
+      </c>
+      <c r="J34" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="24"/>
+      <c r="C35" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H35" s="18"/>
+      <c r="I35" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J35" s="22"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="24"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="24"/>
+      <c r="C37" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I38" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="J38" s="27"/>
+    </row>
+    <row r="39" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" t="str">
+        <f>TRIM(MID(C37,3,2)&amp;" "&amp;MID(D37,3,2)&amp;" "&amp;MID(E37,3,2)&amp;" "&amp;MID(F37,3,2)&amp;" "&amp;MID(G37,3,2)&amp;" "&amp;MID(H37,3,2)&amp;" "&amp;MID(I37,3,2)&amp;" "&amp;MID(J37,3,2))</f>
+        <v>01 06 00 50 FF F6 48 6D</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:F36"/>
+    <mergeCell ref="G35:H36"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:G29"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:F20"/>
+    <mergeCell ref="G19:H20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:G13"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:F4"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6023827-F0D9-469B-8F4C-757A2403C253}">
   <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1721,11 +2486,11 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -1757,34 +2522,34 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="A3" s="24"/>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="18" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="25"/>
+      <c r="A4" s="24"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="6" t="s">
         <v>36</v>
       </c>
@@ -1793,9 +2558,9 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
+      <c r="A5" s="24"/>
       <c r="C5" s="8" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>26</v>
@@ -1813,10 +2578,10 @@
         <v>2</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -1824,11 +2589,11 @@
         <v>13</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="H6" s="28"/>
       <c r="I6" s="28" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J6" s="28"/>
     </row>
@@ -1838,7 +2603,7 @@
       </c>
       <c r="B7" t="str">
         <f>TRIM(MID(C5,3,2)&amp;" "&amp;MID(D5,3,2)&amp;" "&amp;MID(E5,3,2)&amp;" "&amp;MID(F5,3,2)&amp;" "&amp;MID(G5,3,2)&amp;" "&amp;MID(H5,3,2)&amp;" "&amp;MID(I5,3,2)&amp;" "&amp;MID(J5,3,2)&amp;" "&amp;MID(K5,3,2)&amp;" "&amp;MID(L5,3,2)&amp;" "&amp;MID(M5,3,2)&amp;" "&amp;MID(N5,3,2)&amp;" "&amp;MID(O5,3,2)&amp;" "&amp;MID(P5,3,2))</f>
-        <v>05 06 07 D0 00 01 49 03</v>
+        <v>08 06 07 D0 00 01 48 1E</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
@@ -1846,7 +2611,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
@@ -1877,7 +2642,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -1913,32 +2678,32 @@
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="22" t="s">
+      <c r="F14" s="18"/>
+      <c r="G14" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="18" t="s">
+      <c r="H14" s="18"/>
+      <c r="I14" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J14" s="19"/>
+      <c r="J14" s="22"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="25"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1984,11 +2749,11 @@
     <row r="19" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A20" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B21" t="s">
@@ -2020,34 +2785,34 @@
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A22" s="17"/>
-      <c r="C22" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="20" t="s">
+      <c r="A22" s="24"/>
+      <c r="C22" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="23"/>
-      <c r="I22" s="18" t="s">
+      <c r="F22" s="18"/>
+      <c r="G22" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="19"/>
+      <c r="J22" s="22"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="17"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="25"/>
+      <c r="A23" s="24"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="6" t="s">
         <v>36</v>
       </c>
@@ -2056,7 +2821,7 @@
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="17"/>
+      <c r="A24" s="24"/>
       <c r="C24" s="8" t="s">
         <v>2</v>
       </c>
@@ -2067,7 +2832,7 @@
         <v>47</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>5</v>
@@ -2076,10 +2841,10 @@
         <v>2</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -2091,7 +2856,7 @@
       </c>
       <c r="H25" s="28"/>
       <c r="I25" s="28" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J25" s="28"/>
     </row>
@@ -2102,6 +2867,12 @@
       <c r="B26" t="str">
         <f>TRIM(MID(C24,3,2)&amp;" "&amp;MID(D24,3,2)&amp;" "&amp;MID(E24,3,2)&amp;" "&amp;MID(F24,3,2)&amp;" "&amp;MID(G24,3,2)&amp;" "&amp;MID(H24,3,2)&amp;" "&amp;MID(I24,3,2)&amp;" "&amp;MID(J24,3,2)&amp;" "&amp;MID(K24,3,2)&amp;" "&amp;MID(L24,3,2)&amp;" "&amp;MID(M24,3,2)&amp;" "&amp;MID(N24,3,2)&amp;" "&amp;MID(O24,3,2)&amp;" "&amp;MID(P24,3,2))</f>
         <v>01 06 07 D1 00 01 19 47</v>
+      </c>
+      <c r="I26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
@@ -2137,7 +2908,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
@@ -2173,32 +2944,32 @@
       <c r="A33" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33" s="20" t="s">
+      <c r="C33" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="H33" s="23"/>
-      <c r="I33" s="18" t="s">
+      <c r="F33" s="18"/>
+      <c r="G33" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H33" s="18"/>
+      <c r="I33" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J33" s="19"/>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="20"/>
       <c r="I34" s="6" t="s">
         <v>36</v>
       </c>
@@ -2242,6 +3013,19 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="E33:F34"/>
+    <mergeCell ref="G33:H34"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:F23"/>
+    <mergeCell ref="G22:H23"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="A2:A5"/>
@@ -2255,19 +3039,6 @@
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:F15"/>
     <mergeCell ref="G14:H15"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:F23"/>
-    <mergeCell ref="G22:H23"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="E33:F34"/>
-    <mergeCell ref="G33:H34"/>
-    <mergeCell ref="I33:J33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{12BD2609-7915-4B96-828E-BBF6EE96881F}"/>
@@ -2276,7 +3047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{325B5AE2-D427-4080-A06B-A4784F0A1AED}">
   <dimension ref="A1:P38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2291,7 +3062,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -2323,34 +3094,34 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="17"/>
-      <c r="C3" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="A3" s="24"/>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="18"/>
+      <c r="G3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="18" t="s">
+      <c r="H3" s="18"/>
+      <c r="I3" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="22"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="25"/>
+      <c r="A4" s="24"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="6" t="s">
         <v>36</v>
       </c>
@@ -2359,7 +3130,7 @@
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" s="17"/>
+      <c r="A5" s="24"/>
       <c r="C5" s="8" t="s">
         <v>25</v>
       </c>
@@ -2428,7 +3199,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -2461,30 +3232,30 @@
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="20" t="s">
+      <c r="C13" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="18" t="s">
+      <c r="G13" s="18"/>
+      <c r="H13" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="19"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="25"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="6" t="s">
         <v>36</v>
       </c>
@@ -2495,7 +3266,7 @@
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C15" s="5" t="str">
         <f>"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$11,"{",""),"}",""),(COLUMN(A11)-1)*2+1,2)</f>
-        <v>0x07</v>
+        <v>0x01</v>
       </c>
       <c r="D15" s="5" t="str">
         <f t="shared" ref="D15:I15" si="0">"0x"&amp;MID(SUBSTITUTE(SUBSTITUTE($A$11,"{",""),"}",""),(COLUMN(B11)-1)*2+1,2)</f>
@@ -2511,31 +3282,31 @@
       </c>
       <c r="G15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x07</v>
+        <v>0x01</v>
       </c>
       <c r="H15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x71</v>
+        <v>0x79</v>
       </c>
       <c r="I15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>0x86</v>
+        <v>0x84</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.5">
       <c r="A22" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="24" t="s">
         <v>8</v>
       </c>
       <c r="B23" t="s">
@@ -2566,38 +3337,38 @@
         <v>7</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A24" s="17"/>
-      <c r="C24" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="20" t="s">
+      <c r="A24" s="24"/>
+      <c r="C24" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="18"/>
+      <c r="G24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="23"/>
-      <c r="I24" s="18" t="s">
+      <c r="H24" s="18"/>
+      <c r="I24" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J24" s="19"/>
+      <c r="J24" s="22"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A25" s="17"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="25"/>
+      <c r="A25" s="24"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="6" t="s">
         <v>36</v>
       </c>
@@ -2606,7 +3377,7 @@
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A26" s="17"/>
+      <c r="A26" s="24"/>
       <c r="C26" s="8" t="s">
         <v>25</v>
       </c>
@@ -2617,7 +3388,7 @@
         <v>47</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>5</v>
@@ -2626,10 +3397,10 @@
         <v>2</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -2639,7 +3410,7 @@
       <c r="G27" s="28"/>
       <c r="H27" s="28"/>
       <c r="I27" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J27" s="28"/>
     </row>
@@ -2677,7 +3448,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -2710,30 +3481,30 @@
       <c r="A34" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34" s="20" t="s">
+      <c r="C34" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="18" t="s">
+      <c r="F34" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" s="18"/>
+      <c r="H34" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="19"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="25"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="20"/>
       <c r="H35" s="6" t="s">
         <v>36</v>
       </c>
@@ -2760,15 +3531,15 @@
       </c>
       <c r="G36" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>0x02</v>
+        <v>0x01</v>
       </c>
       <c r="H36" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>0x39</v>
+        <v>0x79</v>
       </c>
       <c r="I36" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>0x85</v>
+        <v>0x84</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -2778,6 +3549,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:G35"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:F25"/>
+    <mergeCell ref="G24:H25"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="A2:A5"/>
@@ -2794,22 +3575,12 @@
     <mergeCell ref="F13:G14"/>
     <mergeCell ref="A23:A26"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="E24:F25"/>
-    <mergeCell ref="G24:H25"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:G35"/>
-    <mergeCell ref="H34:I34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{936A926E-67FD-4A17-8CF3-DF8D0187F65D}">
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2855,14 +3626,14 @@
       <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="18" t="s">
+      <c r="F3" s="22"/>
+      <c r="G3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="19"/>
+      <c r="H3" s="22"/>
       <c r="I3" s="6" t="s">
         <v>23</v>
       </c>
